--- a/datenkatalog_up-next.xlsx
+++ b/datenkatalog_up-next.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://htlstp-my.sharepoint.com/personal/20230217_htlstp_at/Documents/HTL3/WMC/upNextFinal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{2D5B1BB8-FCFE-46C6-B56E-66AF77EFD439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{634EA0AA-994B-4F4F-A2CF-AFD1CA83D40F}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="8_{2D5B1BB8-FCFE-46C6-B56E-66AF77EFD439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E69995AA-A581-4A11-B169-F958D010806B}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{8DA0C01B-55EE-402A-A190-D02A9DE7641E}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="2" activeTab="2" xr2:uid="{8DA0C01B-55EE-402A-A190-D02A9DE7641E}"/>
   </bookViews>
   <sheets>
     <sheet name="public_sessions" sheetId="1" r:id="rId1"/>
     <sheet name="private_sessions" sheetId="2" r:id="rId2"/>
+    <sheet name="participants" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="51">
   <si>
     <t>public_sessions</t>
   </si>
@@ -150,7 +151,49 @@
     <t>testParty</t>
   </si>
   <si>
-    <t>int8</t>
+    <t>participants</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>joined_at</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>einmaliger identifier für einen user</t>
+  </si>
+  <si>
+    <t>int4</t>
+  </si>
+  <si>
+    <t>welche rolle hat der user</t>
+  </si>
+  <si>
+    <t>member</t>
+  </si>
+  <si>
+    <t>in welcher session ist dieser user</t>
+  </si>
+  <si>
+    <t>name des users</t>
+  </si>
+  <si>
+    <t>host</t>
+  </si>
+  <si>
+    <t>christosch</t>
+  </si>
+  <si>
+    <t>0c09b24a…</t>
+  </si>
+  <si>
+    <t>hier werden alle users die in sessions, egal ob mode1 oder mode2, gespeichert</t>
   </si>
 </sst>
 </file>
@@ -224,6 +267,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -585,7 +632,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
         <v>21</v>
@@ -735,7 +782,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
         <v>21</v>
@@ -824,4 +871,136 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923C9D38-5DF5-4768-9176-6D9AD19F0F87}">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.85546875" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" customWidth="1"/>
+    <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="1">
+        <v>46175.365358796298</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E10" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>